--- a/content/post/drafts/race-prediction/ladies_simple-model-tests-actual_rmse.xlsx
+++ b/content/post/drafts/race-prediction/ladies_simple-model-tests-actual_rmse.xlsx
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.172385366039012</v>
+        <v>0.173587394986148</v>
       </c>
       <c r="C9" t="n">
-        <v>0.233951976857696</v>
+        <v>0.229738571373278</v>
       </c>
       <c r="D9" t="n">
-        <v>0.254516504173151</v>
+        <v>0.25308283288224</v>
       </c>
       <c r="E9" t="n">
-        <v>0.286809832658344</v>
+        <v>0.288667277357035</v>
       </c>
       <c r="F9" t="n">
-        <v>0.18088856911688</v>
+        <v>0.183115445964998</v>
       </c>
       <c r="G9" t="n">
-        <v>0.164033370200442</v>
+        <v>0.157276345782315</v>
       </c>
       <c r="H9" t="n">
-        <v>0.215430936507587</v>
+        <v>0.214244644724336</v>
       </c>
     </row>
     <row r="10">
